--- a/Month-1/Day-7/Jeddah_ECommerce_Sales_Analysis.xlsx
+++ b/Month-1/Day-7/Jeddah_ECommerce_Sales_Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data-Analysis-and-AI-85Days\Month-1\Day-7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA6F4FD0-57B9-4F67-BCB6-84AB89AFFB3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF8902E-9C41-4F48-9EDB-46FEA4F03D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{FC9FCD97-1A9C-4E75-8C33-95C74EA81365}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="21" r:id="rId3"/>
+    <pivotCache cacheId="2" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -214,10 +214,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="170" formatCode="dd/mm/yyyy;@"/>
-    <numFmt numFmtId="171" formatCode="[$⃁-401]\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="[$⃁-401]\ #,##0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -412,25 +412,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="171" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="171" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -439,232 +446,11 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="22">
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="171" formatCode="[$⃁-401]\ #,##0.00"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="171" formatCode="[$⃁-401]\ #,##0.00"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="dd/mm/yyyy;@"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -680,6 +466,30 @@
         <right/>
         <top/>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$⃁-401]\ #,##0.00"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -702,22 +512,26 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top/>
-        <bottom/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -740,22 +554,27 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="165" formatCode="[$⃁-401]\ #,##0.00"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top/>
-        <bottom/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -778,6 +597,29 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -794,6 +636,114 @@
         </right>
         <top/>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -815,6 +765,26 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <border outline="0">
@@ -824,26 +794,56 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
   </dxfs>
@@ -956,49 +956,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -2080,8 +2038,8 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>28905</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="4" name="القسم">
@@ -2104,7 +2062,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -2193,7 +2151,7 @@
     <cacheField name="رقم الطلب" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1000" maxValue="1019"/>
     </cacheField>
-    <cacheField name="تاريخ الطلب" numFmtId="170">
+    <cacheField name="تاريخ الطلب" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-01-01T00:00:00" maxDate="2026-01-21T00:00:00" count="20">
         <d v="2026-01-06T00:00:00"/>
         <d v="2026-01-03T00:00:00"/>
@@ -2257,13 +2215,13 @@
     <cacheField name="الكمية المباعة(الريال)" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3" maxValue="100"/>
     </cacheField>
-    <cacheField name="سعر الوحدة" numFmtId="171">
+    <cacheField name="سعر الوحدة" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="7" maxValue="250"/>
     </cacheField>
     <cacheField name="المدينة" numFmtId="0">
       <sharedItems/>
     </cacheField>
-    <cacheField name="اجمالي المبيعات(الريال)" numFmtId="171">
+    <cacheField name="اجمالي المبيعات(الريال)" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="180" maxValue="2700"/>
     </cacheField>
   </cacheFields>
@@ -2481,11 +2439,11 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F896FAA5-397F-4885-9681-3DADE1C43FAD}" name="PivotTable7" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F896FAA5-397F-4885-9681-3DADE1C43FAD}" name="PivotTable7" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="M7:N28" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
-    <pivotField numFmtId="170" showAll="0">
+    <pivotField numFmtId="164" showAll="0">
       <items count="21">
         <item x="17"/>
         <item x="11"/>
@@ -2550,9 +2508,9 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="171" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="171" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="2"/>
@@ -2626,7 +2584,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of اجمالي المبيعات(الريال)" fld="7" baseField="0" baseItem="0" numFmtId="171"/>
+    <dataField name="Sum of اجمالي المبيعات(الريال)" fld="7" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="7" format="0" series="1">
@@ -2681,7 +2639,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{38E5957E-9C83-463E-8756-B7ABECDF3653}" name="Table2" displayName="Table2" ref="B3:I24" totalsRowCount="1" headerRowDxfId="0" dataDxfId="18" totalsRowDxfId="9" headerRowBorderDxfId="20" tableBorderDxfId="21" totalsRowBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{38E5957E-9C83-463E-8756-B7ABECDF3653}" name="Table2" displayName="Table2" ref="B3:I24" totalsRowCount="1" headerRowDxfId="21" dataDxfId="19" totalsRowDxfId="17" headerRowBorderDxfId="20" tableBorderDxfId="18" totalsRowBorderDxfId="16">
   <autoFilter ref="B3:I23" xr:uid="{38E5957E-9C83-463E-8756-B7ABECDF3653}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2696,14 +2654,14 @@
     <sortCondition descending="1" ref="I3:I23"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{51C2908A-CAB9-4378-80DE-2A9AFB936FF8}" name="رقم الطلب" totalsRowLabel="Total" dataDxfId="8" totalsRowDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{36A35CCC-FD4E-44F9-940C-3F039164FAC8}" name="تاريخ الطلب" dataDxfId="7" totalsRowDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{E7AA801A-F4E5-4851-86F6-0DD46BD89BD4}" name="المنتج" dataDxfId="6" totalsRowDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{68B26B96-C9A8-4587-9557-35FE46486F3E}" name="القسم" dataDxfId="5" totalsRowDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{4121DBD8-7576-4C4F-B8B0-527D2C105012}" name="الكمية المباعة(الريال)" dataDxfId="4" totalsRowDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{3448A10E-2804-487A-A39D-48F406E8317C}" name="سعر الوحدة" dataDxfId="3" totalsRowDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{2CAFE97A-9D30-4EFA-A5A9-2A2479903057}" name="المدينة" dataDxfId="2" totalsRowDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{9C75ED14-02BC-405F-9FAE-CFEFE462EF17}" name="اجمالي المبيعات(الريال)" totalsRowFunction="sum" dataDxfId="1" totalsRowDxfId="10">
+    <tableColumn id="1" xr3:uid="{51C2908A-CAB9-4378-80DE-2A9AFB936FF8}" name="رقم الطلب" totalsRowLabel="Total" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{36A35CCC-FD4E-44F9-940C-3F039164FAC8}" name="تاريخ الطلب" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{E7AA801A-F4E5-4851-86F6-0DD46BD89BD4}" name="المنتج" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{68B26B96-C9A8-4587-9557-35FE46486F3E}" name="القسم" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{4121DBD8-7576-4C4F-B8B0-527D2C105012}" name="الكمية المباعة(الريال)" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{3448A10E-2804-487A-A39D-48F406E8317C}" name="سعر الوحدة" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{2CAFE97A-9D30-4EFA-A5A9-2A2479903057}" name="المدينة" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{9C75ED14-02BC-405F-9FAE-CFEFE462EF17}" name="اجمالي المبيعات(الريال)" totalsRowFunction="sum" dataDxfId="1" totalsRowDxfId="0">
       <calculatedColumnFormula>F4*G4</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3029,7 +2987,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2780AC97-509C-4DF2-ACD0-8C78518B1D7E}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.54296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
@@ -3040,7 +2998,7 @@
     <col min="7" max="7" width="4.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3063,7 +3021,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1000</v>
       </c>
@@ -3086,7 +3044,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1001</v>
       </c>
@@ -3109,7 +3067,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1001</v>
       </c>
@@ -3132,7 +3090,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1002</v>
       </c>
@@ -3155,7 +3113,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1003</v>
       </c>
@@ -3178,7 +3136,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1004</v>
       </c>
@@ -3201,7 +3159,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1005</v>
       </c>
@@ -3224,7 +3182,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1006</v>
       </c>
@@ -3244,7 +3202,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1007</v>
       </c>
@@ -3264,7 +3222,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1008</v>
       </c>
@@ -3287,7 +3245,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1009</v>
       </c>
@@ -3310,7 +3268,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1010</v>
       </c>
@@ -3333,7 +3291,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1010</v>
       </c>
@@ -3356,7 +3314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1011</v>
       </c>
@@ -3379,7 +3337,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1012</v>
       </c>
@@ -3402,7 +3360,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1013</v>
       </c>
@@ -3425,7 +3383,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1014</v>
       </c>
@@ -3448,7 +3406,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1015</v>
       </c>
@@ -3471,7 +3429,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1016</v>
       </c>
@@ -3494,7 +3452,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1017</v>
       </c>
@@ -3517,7 +3475,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1018</v>
       </c>
@@ -3540,7 +3498,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1019</v>
       </c>
@@ -3568,7 +3526,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E20875B-0C68-4959-B614-5874A7309CA9}">
   <dimension ref="A1:R28"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="14.36328125" bestFit="1" customWidth="1"/>
@@ -3577,48 +3535,48 @@
     <col min="7" max="7" width="10.54296875" customWidth="1"/>
     <col min="8" max="8" width="7.1796875" customWidth="1"/>
     <col min="9" max="9" width="17.6328125" customWidth="1"/>
-    <col min="13" max="13" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="24.6328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.6328125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="P1" s="18" t="s">
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="P1" s="14" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="23.5">
-      <c r="A2" s="8"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="P2" s="15">
+    <row r="2" spans="1:18" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="15"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="P2" s="18">
         <f>GETPIVOTDATA("اجمالي المبيعات(الريال)",$M$7)</f>
         <v>16515</v>
       </c>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="17"/>
-    </row>
-    <row r="3" spans="1:18" ht="16">
-      <c r="A3" s="8"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="20"/>
+    </row>
+    <row r="3" spans="1:18" ht="16" x14ac:dyDescent="0.4">
+      <c r="A3" s="15"/>
       <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
@@ -3643,10 +3601,10 @@
       <c r="I3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="P3" s="14"/>
-    </row>
-    <row r="4" spans="1:18">
-      <c r="A4" s="8"/>
+      <c r="P3" s="13"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A4" s="15"/>
       <c r="B4" s="5">
         <v>1005</v>
       </c>
@@ -3669,12 +3627,12 @@
         <v>9</v>
       </c>
       <c r="I4" s="7">
-        <f>F4*G4</f>
+        <f t="shared" ref="I4:I23" si="0">F4*G4</f>
         <v>2700</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="8"/>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A5" s="15"/>
       <c r="B5" s="5">
         <v>1002</v>
       </c>
@@ -3697,12 +3655,12 @@
         <v>9</v>
       </c>
       <c r="I5" s="7">
-        <f>F5*G5</f>
+        <f t="shared" si="0"/>
         <v>1800</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
-      <c r="A6" s="8"/>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A6" s="15"/>
       <c r="B6" s="5">
         <v>1016</v>
       </c>
@@ -3725,12 +3683,12 @@
         <v>9</v>
       </c>
       <c r="I6" s="7">
-        <f>F6*G6</f>
+        <f t="shared" si="0"/>
         <v>1400</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
-      <c r="A7" s="8"/>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A7" s="15"/>
       <c r="B7" s="5">
         <v>1013</v>
       </c>
@@ -3753,18 +3711,18 @@
         <v>12</v>
       </c>
       <c r="I7" s="7">
-        <f>F7*G7</f>
+        <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="M7" s="9" t="s">
+      <c r="M7" s="8" t="s">
         <v>46</v>
       </c>
       <c r="N7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="8"/>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A8" s="15"/>
       <c r="B8" s="5">
         <v>1017</v>
       </c>
@@ -3787,18 +3745,18 @@
         <v>9</v>
       </c>
       <c r="I8" s="7">
-        <f>F8*G8</f>
+        <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="M8" s="9" t="s">
         <v>18</v>
       </c>
       <c r="N8" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="8"/>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A9" s="15"/>
       <c r="B9" s="5">
         <v>1014</v>
       </c>
@@ -3821,18 +3779,18 @@
         <v>9</v>
       </c>
       <c r="I9" s="7">
-        <f>F9*G9</f>
+        <f t="shared" si="0"/>
         <v>960</v>
       </c>
-      <c r="M9" s="10" t="s">
+      <c r="M9" s="9" t="s">
         <v>37</v>
       </c>
       <c r="N9" s="3">
         <v>720</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="8"/>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A10" s="15"/>
       <c r="B10" s="5">
         <v>1010</v>
       </c>
@@ -3855,18 +3813,18 @@
         <v>9</v>
       </c>
       <c r="I10" s="7">
-        <f>F10*G10</f>
+        <f t="shared" si="0"/>
         <v>750</v>
       </c>
-      <c r="M10" s="10" t="s">
+      <c r="M10" s="9" t="s">
         <v>22</v>
       </c>
       <c r="N10" s="3">
         <v>450</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="8"/>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A11" s="15"/>
       <c r="B11" s="5">
         <v>1011</v>
       </c>
@@ -3889,18 +3847,18 @@
         <v>12</v>
       </c>
       <c r="I11" s="7">
-        <f>F11*G11</f>
+        <f t="shared" si="0"/>
         <v>750</v>
       </c>
-      <c r="M11" s="10" t="s">
+      <c r="M11" s="9" t="s">
         <v>17</v>
       </c>
       <c r="N11" s="3">
         <v>420</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="8"/>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A12" s="15"/>
       <c r="B12" s="5">
         <v>1018</v>
       </c>
@@ -3923,18 +3881,18 @@
         <v>12</v>
       </c>
       <c r="I12" s="7">
-        <f>F12*G12</f>
+        <f t="shared" si="0"/>
         <v>750</v>
       </c>
-      <c r="M12" s="10" t="s">
+      <c r="M12" s="9" t="s">
         <v>38</v>
       </c>
       <c r="N12" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="8"/>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A13" s="15"/>
       <c r="B13" s="5">
         <v>1009</v>
       </c>
@@ -3957,18 +3915,18 @@
         <v>9</v>
       </c>
       <c r="I13" s="7">
-        <f>F13*G13</f>
+        <f t="shared" si="0"/>
         <v>720</v>
       </c>
-      <c r="M13" s="10" t="s">
+      <c r="M13" s="9" t="s">
         <v>39</v>
       </c>
       <c r="N13" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="8"/>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A14" s="15"/>
       <c r="B14" s="5">
         <v>1015</v>
       </c>
@@ -3991,18 +3949,18 @@
         <v>9</v>
       </c>
       <c r="I14" s="7">
-        <f>F14*G14</f>
+        <f t="shared" si="0"/>
         <v>720</v>
       </c>
-      <c r="M14" s="10" t="s">
+      <c r="M14" s="9" t="s">
         <v>15</v>
       </c>
       <c r="N14" s="3">
         <v>240</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="8"/>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A15" s="15"/>
       <c r="B15" s="5">
         <v>1001</v>
       </c>
@@ -4025,18 +3983,18 @@
         <v>12</v>
       </c>
       <c r="I15" s="7">
-        <f>F15*G15</f>
+        <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="M15" s="10" t="s">
+      <c r="M15" s="9" t="s">
         <v>7</v>
       </c>
       <c r="N15" s="3">
         <v>350</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="8"/>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A16" s="15"/>
       <c r="B16" s="5">
         <v>1008</v>
       </c>
@@ -4059,18 +4017,18 @@
         <v>9</v>
       </c>
       <c r="I16" s="7">
-        <f>F16*G16</f>
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="M16" s="10" t="s">
+      <c r="M16" s="9" t="s">
         <v>23</v>
       </c>
       <c r="N16" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="8"/>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A17" s="15"/>
       <c r="B17" s="5">
         <v>1007</v>
       </c>
@@ -4093,18 +4051,18 @@
         <v>12</v>
       </c>
       <c r="I17" s="7">
-        <f>F17*G17</f>
+        <f t="shared" si="0"/>
         <v>450</v>
       </c>
-      <c r="M17" s="10" t="s">
+      <c r="M17" s="9" t="s">
         <v>21</v>
       </c>
       <c r="N17" s="3">
         <v>375</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="8"/>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A18" s="15"/>
       <c r="B18" s="5">
         <v>1012</v>
       </c>
@@ -4127,18 +4085,18 @@
         <v>9</v>
       </c>
       <c r="I18" s="7">
-        <f>F18*G18</f>
+        <f t="shared" si="0"/>
         <v>450</v>
       </c>
-      <c r="M18" s="10" t="s">
+      <c r="M18" s="9" t="s">
         <v>35</v>
       </c>
       <c r="N18" s="3">
         <v>960</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="8"/>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A19" s="15"/>
       <c r="B19" s="5">
         <v>1004</v>
       </c>
@@ -4161,18 +4119,18 @@
         <v>9</v>
       </c>
       <c r="I19" s="7">
-        <f>F19*G19</f>
+        <f t="shared" si="0"/>
         <v>420</v>
       </c>
-      <c r="M19" s="10" t="s">
+      <c r="M19" s="9" t="s">
         <v>33</v>
       </c>
       <c r="N19" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="8"/>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A20" s="15"/>
       <c r="B20" s="5">
         <v>1006</v>
       </c>
@@ -4195,18 +4153,18 @@
         <v>9</v>
       </c>
       <c r="I20" s="7">
-        <f>F20*G20</f>
+        <f t="shared" si="0"/>
         <v>375</v>
       </c>
-      <c r="M20" s="10" t="s">
+      <c r="M20" s="9" t="s">
         <v>41</v>
       </c>
       <c r="N20" s="3">
         <v>180</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="8"/>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A21" s="15"/>
       <c r="B21" s="5">
         <v>1000</v>
       </c>
@@ -4229,18 +4187,18 @@
         <v>9</v>
       </c>
       <c r="I21" s="7">
-        <f>F21*G21</f>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
-      <c r="M21" s="10" t="s">
+      <c r="M21" s="9" t="s">
         <v>25</v>
       </c>
       <c r="N21" s="3">
         <v>720</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="8"/>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A22" s="15"/>
       <c r="B22" s="5">
         <v>1003</v>
       </c>
@@ -4263,18 +4221,18 @@
         <v>16</v>
       </c>
       <c r="I22" s="7">
-        <f>F22*G22</f>
+        <f t="shared" si="0"/>
         <v>240</v>
       </c>
-      <c r="M22" s="10" t="s">
+      <c r="M22" s="9" t="s">
         <v>10</v>
       </c>
       <c r="N22" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="8"/>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A23" s="15"/>
       <c r="B23" s="5">
         <v>1019</v>
       </c>
@@ -4297,64 +4255,64 @@
         <v>9</v>
       </c>
       <c r="I23" s="7">
-        <f>F23*G23</f>
+        <f t="shared" si="0"/>
         <v>180</v>
       </c>
-      <c r="M23" s="10" t="s">
+      <c r="M23" s="9" t="s">
         <v>30</v>
       </c>
       <c r="N23" s="3">
         <v>750</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
-      <c r="B24" s="11" t="s">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B24" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="13">
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="12">
         <f>SUBTOTAL(109,Table2[اجمالي المبيعات(الريال)])</f>
         <v>16515</v>
       </c>
-      <c r="M24" s="10" t="s">
+      <c r="M24" s="9" t="s">
         <v>28</v>
       </c>
       <c r="N24" s="3">
         <v>750</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="H25" s="4"/>
-      <c r="M25" s="10" t="s">
+      <c r="M25" s="9" t="s">
         <v>32</v>
       </c>
       <c r="N25" s="3">
         <v>450</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
-      <c r="M26" s="10" t="s">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="M26" s="9" t="s">
         <v>40</v>
       </c>
       <c r="N26" s="3">
         <v>750</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
-      <c r="M27" s="10" t="s">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="M27" s="9" t="s">
         <v>13</v>
       </c>
       <c r="N27" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
-      <c r="M28" s="10" t="s">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="M28" s="9" t="s">
         <v>47</v>
       </c>
       <c r="N28" s="3">
@@ -4369,6 +4327,13 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I4:I23">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -4380,13 +4345,6 @@
           <x14:id>{D85E7782-0346-4D59-8703-93D31FA7B319}</x14:id>
         </ext>
       </extLst>
-    </cfRule>
-    <cfRule type="iconSet" priority="1">
-      <iconSet iconSet="3Arrows">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="33"/>
-        <cfvo type="percent" val="67"/>
-      </iconSet>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4422,6 +4380,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C75CCA8C93D93A43A1AC488E2F0D8821" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1e8fad8455d7b5c89a93d4178a3fc1c9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d6bf451c-e3aa-4dd1-b5a6-a95183d31bdf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8408199938cbb8869539c7a2b993ecc3" ns3:_="">
     <xsd:import namespace="d6bf451c-e3aa-4dd1-b5a6-a95183d31bdf"/>
@@ -4565,15 +4532,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -4581,6 +4539,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EA3F5F5-320B-42BB-A4A1-9F4DDD8347CE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C620909-6114-4022-B6E2-7D1B50CD5B18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4598,26 +4564,18 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EA3F5F5-320B-42BB-A4A1-9F4DDD8347CE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2258CF38-D835-4172-80BB-976D11FA6727}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="d6bf451c-e3aa-4dd1-b5a6-a95183d31bdf"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>